--- a/Projects.xlsx
+++ b/Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MD\Study\Тестирование Яндекс Практикум\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYProjects\YandexTesting\Sprint_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD781DAC-BD3B-4EA8-9576-9470B9CE4883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9183D257-D1EF-4AD6-A5B2-4547CEAEDC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2784" yWindow="108" windowWidth="20256" windowHeight="13512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3432" yWindow="48" windowWidth="14916" windowHeight="13512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Авт5" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="45">
   <si>
     <t>Комментарий</t>
   </si>
@@ -139,6 +139,39 @@
     <t xml:space="preserve">Вот только в нашей теории написан пример остановки кода на 3 секунды: "from selenium.webdriver.support.wait import WebDriverWait
 # Остановить тест на 3 секунды
 WebDriverWait(driver, 3) ". А в реальности это так не работает, да. В этом курсе встречаются такие вещи, к сожалению. </t>
+  </si>
+  <si>
+    <t>5-3</t>
+  </si>
+  <si>
+    <t>Нужно исправить: в тесты можно передавать обе фикстуры, а не вкладывать одну в другую. Может быть нужен сценарий, когда логин происходит после каких-то действий. Вложенных фикстур быть не должно</t>
+  </si>
+  <si>
+    <t>Нужно исправить: весь закомментированный код должен быть убран</t>
+  </si>
+  <si>
+    <t>Нужно исправить: некорректное ожидание, нужно поправить как по всему проекту или убрать</t>
+  </si>
+  <si>
+    <t>locators.py</t>
+  </si>
+  <si>
+    <t>Нужно исправить: воспользуйся фикстурой</t>
+  </si>
+  <si>
+    <t>tests/test_personal_account.py</t>
+  </si>
+  <si>
+    <t>Нужно убрать лишние импорты, оставшиеся от использования sleep</t>
+  </si>
+  <si>
+    <t>и в этом файле, и в еще одном тоже</t>
+  </si>
+  <si>
+    <t>и sleep, и By</t>
+  </si>
+  <si>
+    <t>Я пробовала сделать независимую фикстуру логина без создания драйвера. Но встал вопрос передачи в нее созданного драйвера. Пробовала использовать request.cls.driver - но для этого необходима переменная класса с драйвером до начала выполнения теста и фикстур. Пробовала через params, но там, опять же, необходим драйвер до начала выполнения. В общем, сделать фикстуру, чтобы вызвать ее из середины теста и передать ей еще параметр, я не смогла. Поэтому сделала метод логина, который и использую в тестах. Если ты мне объяснишь, как надо было делать эту фикстуру логина независимо от всех, буду благодарна.</t>
   </si>
 </sst>
 </file>
@@ -189,7 +222,119 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -256,15 +401,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F65A0EE-D91F-4A46-943E-19EA39101F17}" name="Table1" displayName="Table1" ref="C2:H18" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="C2:H18" xr:uid="{4F65A0EE-D91F-4A46-943E-19EA39101F17}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F65A0EE-D91F-4A46-943E-19EA39101F17}" name="Table1" displayName="Table1" ref="C2:H22" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="C2:H22" xr:uid="{4F65A0EE-D91F-4A46-943E-19EA39101F17}"/>
   <tableColumns count="6">
-    <tableColumn id="6" xr3:uid="{091025B8-86A1-42F1-BB87-62C4D04BE491}" name="Проект-сдача" dataDxfId="9"/>
-    <tableColumn id="1" xr3:uid="{1EBE394D-5A7A-48DD-81F2-B2EFE99F3F4A}" name="Файл" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{2AEAB213-1151-4A8C-83D9-5EFA107F49F5}" name="Комментарий" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{8C42F816-2DD8-498C-A76E-A7163CAE9E33}" name="Исправлено" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{7B13A394-486B-453F-AE22-2504C0E5CFBA}" name="Ответ" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{99061786-2D74-4346-9CD4-D8A59A363AE6}" name="Прочее" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{091025B8-86A1-42F1-BB87-62C4D04BE491}" name="Проект-сдача" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{1EBE394D-5A7A-48DD-81F2-B2EFE99F3F4A}" name="Файл" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{2AEAB213-1151-4A8C-83D9-5EFA107F49F5}" name="Комментарий" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{8C42F816-2DD8-498C-A76E-A7163CAE9E33}" name="Исправлено" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{7B13A394-486B-453F-AE22-2504C0E5CFBA}" name="Ответ" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{99061786-2D74-4346-9CD4-D8A59A363AE6}" name="Прочее" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -533,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:K17"/>
+  <dimension ref="C2:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
@@ -698,7 +843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
@@ -760,7 +905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="3:8" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" ht="144" x14ac:dyDescent="0.3">
       <c r="C16" s="3" t="s">
         <v>21</v>
       </c>
@@ -777,21 +922,105 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="3"/>
+    <row r="17" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="C17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="C18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F3:F18">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="F3:F22">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"не нужно"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"да"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>"вопрос"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"нет"</formula>
     </cfRule>
   </conditionalFormatting>
